--- a/public/samples/remains/ptfecayong.xlsx
+++ b/public/samples/remains/ptfecayong.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leanhtu/Desktop/merge/project_freelance/KHO/Kho còn lại/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F57FA0A-1DE6-4C4D-9FC8-C6D4D741E144}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="15440" xr2:uid="{A5994B5F-8B4D-1541-84AF-2416DE1D466C}"/>
+    <workbookView windowWidth="28800" windowHeight="12040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="195">
   <si>
     <t>Tồn</t>
   </si>
@@ -55,6 +44,9 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Đơn giá</t>
   </si>
   <si>
     <t>HPP 0402</t>
@@ -613,30 +605,371 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="0.000"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="d&quot;/&quot;m&quot;/&quot;yyyy"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -644,28 +977,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -714,7 +1333,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -747,26 +1366,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -799,23 +1401,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -957,29 +1542,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DF5EC47-DEB5-2D40-BB8D-9D344C0D6D04}">
-  <dimension ref="A1:K164"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L164"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.8"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="4:10">
       <c r="D1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="I1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="I1" s="4"/>
       <c r="J1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -995,7 +1575,7 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G2" t="s">
@@ -1004,25 +1584,28 @@
       <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
         <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
@@ -1030,34 +1613,34 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>200</v>
       </c>
       <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="4">
+        <v>44350</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3">
-        <v>44350</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>1.8</v>
@@ -1065,32 +1648,32 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>3.6</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I4" s="4"/>
       <c r="J4">
         <v>2</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="3">
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="1">
         <v>20</v>
@@ -1098,32 +1681,32 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I5" s="4"/>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D6" s="1">
         <v>40</v>
@@ -1131,32 +1714,32 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I6" s="4"/>
       <c r="J6">
         <v>2</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="3">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -1164,32 +1747,32 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I7" s="4"/>
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D8" s="1">
         <v>27</v>
@@ -1197,32 +1780,32 @@
       <c r="E8">
         <v>3</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I8" s="4"/>
       <c r="J8">
         <v>3</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="3">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
@@ -1230,32 +1813,32 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D10" s="1">
         <v>15</v>
@@ -1263,32 +1846,32 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I10" s="4"/>
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
@@ -1296,34 +1879,34 @@
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>100</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3">
+        <v>15</v>
+      </c>
+      <c r="I11" s="4">
         <v>44350</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="1">
         <v>1.65</v>
@@ -1331,32 +1914,32 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>1.65</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I12" s="4"/>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>1.65</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D13" s="1">
         <v>50</v>
@@ -1364,32 +1947,32 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I13" s="4"/>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -1397,32 +1980,32 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I14" s="4"/>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -1430,32 +2013,32 @@
       <c r="E15">
         <v>19</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>19</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I15" s="4"/>
       <c r="J15">
         <v>19</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="3">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="4" t="s">
         <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="D16" s="1">
         <v>0.1</v>
@@ -1463,32 +2046,32 @@
       <c r="E16">
         <v>17</v>
       </c>
-      <c r="F16" s="2">
-        <v>1.7000000000000002</v>
+      <c r="F16" s="3">
+        <v>1.7</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I16" s="4"/>
       <c r="J16">
         <v>17</v>
       </c>
-      <c r="K16" s="2">
-        <v>1.7000000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K16" s="3">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -1496,32 +2079,32 @@
       <c r="E17">
         <v>5</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I17" s="4"/>
       <c r="J17">
         <v>5</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D18" s="1">
         <v>0.41</v>
@@ -1529,32 +2112,32 @@
       <c r="E18">
         <v>34</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>13.94</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I18" s="4"/>
       <c r="J18">
         <v>34</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="3">
         <v>13.94</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D19" s="1">
         <v>0.1</v>
@@ -1562,98 +2145,98 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>0.1</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I19" s="4"/>
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="3"/>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
       <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.14</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0.14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
       <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D22" s="1">
         <v>0.13</v>
@@ -1661,32 +2244,32 @@
       <c r="E22">
         <v>4</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>0.52</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I22" s="4"/>
       <c r="J22">
         <v>4</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="3">
         <v>0.52</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D23" s="1">
         <v>0.11</v>
@@ -1694,32 +2277,32 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>0.11</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I23" s="4"/>
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="3">
         <v>0.11</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D24" s="1">
         <v>0.1</v>
@@ -1727,32 +2310,32 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>0.1</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I24" s="4"/>
       <c r="J24">
         <v>1</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -1760,65 +2343,65 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I25" s="4"/>
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D27" s="1">
         <v>0.75</v>
@@ -1826,65 +2409,65 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>0.75</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I27" s="4"/>
       <c r="J27">
         <v>1</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" s="1">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
-      <c r="F28" s="2">
-        <v>0.56000000000000005</v>
+      <c r="F28" s="3">
+        <v>0.56</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I28" s="4"/>
       <c r="J28">
         <v>2</v>
       </c>
-      <c r="K28" s="2">
-        <v>0.56000000000000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -1892,32 +2475,32 @@
       <c r="E29">
         <v>2</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I29" s="4"/>
       <c r="J29">
         <v>2</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -1925,32 +2508,32 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I30" s="4"/>
       <c r="J30">
         <v>1</v>
       </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -1958,32 +2541,32 @@
       <c r="E31">
         <v>7</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>7</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I31" s="4"/>
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D32" s="1">
         <v>0.7</v>
@@ -1991,65 +2574,65 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>0.7</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I32" s="4"/>
       <c r="J32">
         <v>0</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" s="2">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33">
-        <v>1</v>
-      </c>
-      <c r="K33" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>47</v>
-      </c>
       <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D34" s="1">
         <v>0.5</v>
@@ -2057,65 +2640,65 @@
       <c r="E34">
         <v>5</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>2.5</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I34" s="4"/>
       <c r="J34">
         <v>5</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="3">
         <v>2.5</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="C35" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D35" s="1">
-        <v>0.29499999999999998</v>
+        <v>0.295</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35" s="2">
-        <v>0.29499999999999998</v>
+      <c r="F35" s="3">
+        <v>0.295</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I35" s="4"/>
       <c r="J35">
         <v>1</v>
       </c>
-      <c r="K35" s="2">
-        <v>0.29499999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D36" s="1">
         <v>0.3</v>
@@ -2123,65 +2706,65 @@
       <c r="E36">
         <v>1</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>0.3</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
-      </c>
-      <c r="I36" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I36" s="4"/>
       <c r="J36">
         <v>1</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.295</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0.295</v>
+      </c>
+      <c r="G37" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0.295</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="1">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="G37" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37" s="2">
-        <v>0.29499999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
       <c r="B38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D38" s="1">
         <v>0.31</v>
@@ -2189,65 +2772,65 @@
       <c r="E38">
         <v>1</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>0.31</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I38" s="4"/>
       <c r="J38">
         <v>1</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="3">
         <v>0.31</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="C39" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="D39" s="1">
-        <v>0.30199999999999999</v>
+        <v>0.302</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
-      <c r="F39" s="2">
-        <v>0.30199999999999999</v>
+      <c r="F39" s="3">
+        <v>0.302</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I39" s="4"/>
       <c r="J39">
         <v>1</v>
       </c>
-      <c r="K39" s="2">
-        <v>0.30199999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K39" s="3">
+        <v>0.302</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="D40" s="1">
         <v>0.3</v>
@@ -2255,65 +2838,65 @@
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>0.6</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
-      </c>
-      <c r="I40" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I40" s="4"/>
       <c r="J40">
         <v>2</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0.305</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3">
+        <v>0.305</v>
+      </c>
+      <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
         <v>51</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="B42" t="s">
         <v>52</v>
       </c>
-      <c r="D41" s="1">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="G41" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" t="s">
-        <v>14</v>
-      </c>
-      <c r="I41" s="3"/>
-      <c r="J41">
-        <v>1</v>
-      </c>
-      <c r="K41" s="2">
-        <v>0.30499999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>52</v>
+      <c r="C42" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D42" s="1">
         <v>0.32</v>
@@ -2321,32 +2904,32 @@
       <c r="E42">
         <v>1</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>0.32</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I42" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I42" s="4"/>
       <c r="J42">
         <v>1</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="3">
         <v>0.32</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="D43" s="1">
         <v>0.09</v>
@@ -2354,32 +2937,32 @@
       <c r="E43">
         <v>1</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>0.09</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
-        <v>14</v>
-      </c>
-      <c r="I43" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I43" s="4"/>
       <c r="J43">
         <v>1</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="3">
         <v>0.09</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="4" t="s">
         <v>62</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="D44" s="1">
         <v>0.21</v>
@@ -2387,32 +2970,32 @@
       <c r="E44">
         <v>4</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>0.84</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I44" s="4"/>
       <c r="J44">
         <v>4</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="3">
         <v>0.84</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="D45" s="1">
         <v>0.15</v>
@@ -2420,32 +3003,32 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>0.15</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I45" s="4"/>
       <c r="J45">
         <v>1</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D46" s="1">
         <v>0.15</v>
@@ -2453,32 +3036,32 @@
       <c r="E46">
         <v>8</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>1.2</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I46" s="4"/>
       <c r="J46">
         <v>8</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="D47" s="1">
         <v>0.15</v>
@@ -2486,32 +3069,32 @@
       <c r="E47">
         <v>8</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>1.2</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I47" s="4"/>
       <c r="J47">
         <v>8</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="D48" s="1">
         <v>0.05</v>
@@ -2519,32 +3102,32 @@
       <c r="E48">
         <v>1</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <v>0.05</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I48" s="4"/>
       <c r="J48">
         <v>1</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="D49" s="1">
         <v>0.35</v>
@@ -2552,32 +3135,32 @@
       <c r="E49">
         <v>1</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>0.35</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I49" s="4"/>
       <c r="J49">
         <v>1</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="3">
         <v>0.35</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>74</v>
+        <v>62</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="D50" s="1">
         <v>0.03</v>
@@ -2585,32 +3168,32 @@
       <c r="E50">
         <v>2</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="3">
         <v>0.06</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I50" s="4"/>
       <c r="J50">
         <v>2</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="3">
         <v>0.06</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="D51" s="1">
         <v>0.18</v>
@@ -2618,32 +3201,32 @@
       <c r="E51">
         <v>1</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <v>0.18</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I51" s="4"/>
       <c r="J51">
         <v>1</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3">
         <v>0.18</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>78</v>
+        <v>62</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D52" s="1">
         <v>0.1</v>
@@ -2651,32 +3234,32 @@
       <c r="E52">
         <v>1</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="3">
         <v>0.1</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I52" s="4"/>
       <c r="J52">
         <v>1</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>80</v>
+        <v>62</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="D53" s="1">
         <v>0.15</v>
@@ -2684,32 +3267,32 @@
       <c r="E53">
         <v>8</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <v>1.2</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H53" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I53" s="4"/>
       <c r="J53">
         <v>8</v>
       </c>
-      <c r="K53" s="2">
+      <c r="K53" s="3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>82</v>
+        <v>62</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="D54" s="1">
         <v>0.15</v>
@@ -2717,32 +3300,32 @@
       <c r="E54">
         <v>10</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="3">
         <v>1.5</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I54" s="4"/>
       <c r="J54">
         <v>10</v>
       </c>
-      <c r="K54" s="2">
+      <c r="K54" s="3">
         <v>1.5</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>84</v>
+        <v>62</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="D55" s="1">
         <v>0.1</v>
@@ -2750,32 +3333,32 @@
       <c r="E55">
         <v>42</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <v>4.2</v>
       </c>
       <c r="G55" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I55" s="4"/>
       <c r="J55">
         <v>24</v>
       </c>
-      <c r="K55" s="2">
-        <v>2.4000000000000004</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K55" s="3">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>87</v>
+        <v>62</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="D56" s="1">
         <v>0.15</v>
@@ -2783,164 +3366,164 @@
       <c r="E56">
         <v>2</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="3">
         <v>0.3</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I56" s="4"/>
       <c r="J56">
         <v>2</v>
       </c>
-      <c r="K56" s="2">
+      <c r="K56" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="4" t="s">
         <v>90</v>
       </c>
+      <c r="C57" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D57" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="E57">
         <v>5</v>
       </c>
-      <c r="F57" s="2">
-        <v>0.51500000000000001</v>
+      <c r="F57" s="3">
+        <v>0.515</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I57" s="4"/>
       <c r="J57">
         <v>5</v>
       </c>
-      <c r="K57" s="2">
-        <v>0.51500000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3">
+        <v>0.515</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D58" s="1">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="E58">
         <v>5</v>
       </c>
-      <c r="F58" s="2">
-        <v>8.5000000000000006E-2</v>
+      <c r="F58" s="3">
+        <v>0.085</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I58" s="4"/>
       <c r="J58">
         <v>5</v>
       </c>
-      <c r="K58" s="2">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3">
+        <v>0.085</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D59" s="1">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="E59">
         <v>1</v>
       </c>
-      <c r="F59" s="2">
-        <v>0.10299999999999999</v>
+      <c r="F59" s="3">
+        <v>0.103</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I59" s="4"/>
       <c r="J59">
         <v>1</v>
       </c>
-      <c r="K59" s="2">
-        <v>0.10299999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="D60" s="1">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60" s="2">
-        <v>1.7000000000000001E-2</v>
+      <c r="F60" s="3">
+        <v>0.017</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I60" s="4"/>
       <c r="J60">
         <v>0</v>
       </c>
-      <c r="K60" s="2">
+      <c r="K60" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D61" s="1">
         <v>0.154</v>
@@ -2948,98 +3531,98 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="3">
         <v>0.154</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
-      </c>
-      <c r="I61" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I61" s="4"/>
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="K61" s="2">
+      <c r="K61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D62" s="1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
-      <c r="F62" s="2">
-        <v>8.6999999999999994E-2</v>
+      <c r="F62" s="3">
+        <v>0.087</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I62" s="4"/>
       <c r="J62">
         <v>0</v>
       </c>
-      <c r="K62" s="2">
+      <c r="K62" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D63" s="1">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
-      <c r="F63" s="2">
-        <v>2.1999999999999999E-2</v>
+      <c r="F63" s="3">
+        <v>0.022</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I63" s="4"/>
       <c r="J63">
         <v>1</v>
       </c>
-      <c r="K63" s="2">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0.022</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B64" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D64" s="1">
         <v>0.154</v>
@@ -3047,65 +3630,65 @@
       <c r="E64">
         <v>1</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="3">
         <v>0.154</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H64" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I64" s="4"/>
       <c r="J64">
         <v>0</v>
       </c>
-      <c r="K64" s="2">
+      <c r="K64" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>89</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="D65" s="1">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
-      <c r="F65" s="2">
-        <v>5.5E-2</v>
+      <c r="F65" s="3">
+        <v>0.055</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I65" s="4"/>
       <c r="J65">
         <v>1</v>
       </c>
-      <c r="K65" s="2">
-        <v>5.5E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D66" s="1">
         <v>0.89</v>
@@ -3113,32 +3696,32 @@
       <c r="E66">
         <v>1</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="3">
         <v>0.89</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I66" s="4"/>
       <c r="J66">
         <v>1</v>
       </c>
-      <c r="K66" s="2">
+      <c r="K66" s="3">
         <v>0.89</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>104</v>
+        <v>90</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="D67" s="1">
         <v>0.04</v>
@@ -3146,65 +3729,65 @@
       <c r="E67">
         <v>1</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="3">
         <v>0.04</v>
       </c>
       <c r="G67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H67" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I67" s="4"/>
       <c r="J67">
         <v>1</v>
       </c>
-      <c r="K67" s="2">
+      <c r="K67" s="3">
         <v>0.04</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>106</v>
+        <v>90</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="D68" s="1">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
-      <c r="F68" s="2">
-        <v>5.3999999999999999E-2</v>
+      <c r="F68" s="3">
+        <v>0.054</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
-      </c>
-      <c r="I68" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I68" s="4"/>
       <c r="J68">
         <v>1</v>
       </c>
-      <c r="K68" s="2">
-        <v>5.3999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>108</v>
+        <v>90</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D69" s="1">
         <v>0.155</v>
@@ -3212,32 +3795,32 @@
       <c r="E69">
         <v>1</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="3">
         <v>0.155</v>
       </c>
       <c r="G69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H69" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I69" s="4"/>
       <c r="J69">
         <v>1</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69" s="3">
         <v>0.155</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>110</v>
+        <v>90</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="D70" s="1">
         <v>0.09</v>
@@ -3245,65 +3828,65 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="3">
         <v>0.09</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I70" s="4"/>
       <c r="J70">
         <v>0</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
-      </c>
-      <c r="C71" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0.305</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" s="3">
+        <v>0.305</v>
+      </c>
+      <c r="G71" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0.305</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
         <v>112</v>
       </c>
-      <c r="D71" s="1">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71" s="2">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="G71" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" s="3"/>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71" s="2">
-        <v>0.30499999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>111</v>
-      </c>
       <c r="B72" t="s">
-        <v>89</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>112</v>
+        <v>90</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="D72" s="1">
         <v>0.3</v>
@@ -3311,32 +3894,32 @@
       <c r="E72">
         <v>1</v>
       </c>
-      <c r="F72" s="2">
+      <c r="F72" s="3">
         <v>0.3</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H72" t="s">
-        <v>14</v>
-      </c>
-      <c r="I72" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I72" s="4"/>
       <c r="J72">
         <v>1</v>
       </c>
-      <c r="K72" s="2">
+      <c r="K72" s="3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>112</v>
+        <v>90</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="D73" s="1">
         <v>0.15</v>
@@ -3344,32 +3927,32 @@
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="F73" s="2">
+      <c r="F73" s="3">
         <v>0.15</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>14</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I73" s="4"/>
       <c r="J73">
         <v>1</v>
       </c>
-      <c r="K73" s="2">
+      <c r="K73" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="D74" s="1">
         <v>0.86</v>
@@ -3377,32 +3960,32 @@
       <c r="E74">
         <v>1</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="3">
         <v>0.86</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>14</v>
-      </c>
-      <c r="I74" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I74" s="4"/>
       <c r="J74">
         <v>1</v>
       </c>
-      <c r="K74" s="2">
+      <c r="K74" s="3">
         <v>0.86</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -3410,32 +3993,32 @@
       <c r="E75">
         <v>1</v>
       </c>
-      <c r="F75" s="2">
+      <c r="F75" s="3">
         <v>1</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H75" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I75" s="4"/>
       <c r="J75">
         <v>1</v>
       </c>
-      <c r="K75" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>118</v>
+        <v>90</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="D76" s="1">
         <v>0.89</v>
@@ -3443,32 +4026,32 @@
       <c r="E76">
         <v>1</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="3">
         <v>0.89</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>14</v>
-      </c>
-      <c r="I76" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I76" s="4"/>
       <c r="J76">
         <v>1</v>
       </c>
-      <c r="K76" s="2">
+      <c r="K76" s="3">
         <v>0.89</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B77" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" s="2" t="s">
         <v>121</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -3476,32 +4059,32 @@
       <c r="E77">
         <v>4</v>
       </c>
-      <c r="F77" s="2">
+      <c r="F77" s="3">
         <v>4</v>
       </c>
       <c r="G77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H77" t="s">
-        <v>14</v>
-      </c>
-      <c r="I77" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I77" s="4"/>
       <c r="J77">
         <v>4</v>
       </c>
-      <c r="K77" s="2">
+      <c r="K77" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B78" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="D78" s="1">
         <v>0.8</v>
@@ -3509,32 +4092,32 @@
       <c r="E78">
         <v>1</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="3">
         <v>0.8</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>14</v>
-      </c>
-      <c r="I78" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I78" s="4"/>
       <c r="J78">
         <v>1</v>
       </c>
-      <c r="K78" s="2">
+      <c r="K78" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B79" t="s">
-        <v>120</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>124</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
@@ -3542,32 +4125,32 @@
       <c r="E79">
         <v>4</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="3">
         <v>4</v>
       </c>
       <c r="G79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>14</v>
-      </c>
-      <c r="I79" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I79" s="4"/>
       <c r="J79">
         <v>4</v>
       </c>
-      <c r="K79" s="2">
+      <c r="K79" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B80" t="s">
-        <v>120</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -3575,32 +4158,32 @@
       <c r="E80">
         <v>100</v>
       </c>
-      <c r="F80" s="2">
+      <c r="F80" s="3">
         <v>100</v>
       </c>
       <c r="G80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
-      </c>
-      <c r="I80" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I80" s="4"/>
       <c r="J80">
         <v>75</v>
       </c>
-      <c r="K80" s="2">
+      <c r="K80" s="3">
         <v>75</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="D81" s="1">
         <v>0.9</v>
@@ -3608,32 +4191,32 @@
       <c r="E81">
         <v>2</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="3">
         <v>1.8</v>
       </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H81" t="s">
-        <v>14</v>
-      </c>
-      <c r="I81" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I81" s="4"/>
       <c r="J81">
         <v>1</v>
       </c>
-      <c r="K81" s="2">
+      <c r="K81" s="3">
         <v>0.9</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B82" t="s">
-        <v>120</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="D82" s="1">
         <v>0.34</v>
@@ -3641,32 +4224,32 @@
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="3">
         <v>0.34</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H82" t="s">
-        <v>14</v>
-      </c>
-      <c r="I82" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I82" s="4"/>
       <c r="J82">
         <v>1</v>
       </c>
-      <c r="K82" s="2">
+      <c r="K82" s="3">
         <v>0.34</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B83" t="s">
-        <v>120</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -3674,32 +4257,32 @@
       <c r="E83">
         <v>4</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="3">
         <v>4</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>14</v>
-      </c>
-      <c r="I83" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I83" s="4"/>
       <c r="J83">
         <v>4</v>
       </c>
-      <c r="K83" s="2">
+      <c r="K83" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -3707,32 +4290,32 @@
       <c r="E84">
         <v>4</v>
       </c>
-      <c r="F84" s="2">
+      <c r="F84" s="3">
         <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H84" t="s">
-        <v>14</v>
-      </c>
-      <c r="I84" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I84" s="4"/>
       <c r="J84">
         <v>4</v>
       </c>
-      <c r="K84" s="2">
+      <c r="K84" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B85" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="D85" s="1">
         <v>0.75</v>
@@ -3740,32 +4323,32 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="3">
         <v>0.75</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H85" t="s">
-        <v>14</v>
-      </c>
-      <c r="I85" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I85" s="4"/>
       <c r="J85">
         <v>1</v>
       </c>
-      <c r="K85" s="2">
+      <c r="K85" s="3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>131</v>
+        <v>121</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="D86" s="1">
         <v>0.18</v>
@@ -3773,32 +4356,32 @@
       <c r="E86">
         <v>1</v>
       </c>
-      <c r="F86" s="2">
+      <c r="F86" s="3">
         <v>0.18</v>
       </c>
       <c r="G86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H86" t="s">
-        <v>14</v>
-      </c>
-      <c r="I86" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I86" s="4"/>
       <c r="J86">
         <v>1</v>
       </c>
-      <c r="K86" s="2">
+      <c r="K86" s="3">
         <v>0.18</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
@@ -3806,32 +4389,32 @@
       <c r="E87">
         <v>39</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="3">
         <v>39</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>14</v>
-      </c>
-      <c r="I87" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I87" s="4"/>
       <c r="J87">
         <v>35</v>
       </c>
-      <c r="K87" s="2">
+      <c r="K87" s="3">
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>120</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -3839,65 +4422,65 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="3">
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H88" t="s">
-        <v>14</v>
-      </c>
-      <c r="I88" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I88" s="4"/>
       <c r="J88">
         <v>13</v>
       </c>
-      <c r="K88" s="2">
+      <c r="K88" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B89" t="s">
-        <v>120</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D89" s="1">
-        <v>0.81499999999999995</v>
+        <v>0.815</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="F89" s="2">
-        <v>0.81499999999999995</v>
+      <c r="F89" s="3">
+        <v>0.815</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s">
-        <v>14</v>
-      </c>
-      <c r="I89" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I89" s="4"/>
       <c r="J89">
         <v>0</v>
       </c>
-      <c r="K89" s="2">
+      <c r="K89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
-        <v>120</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D90" s="1">
         <v>0.75</v>
@@ -3905,32 +4488,32 @@
       <c r="E90">
         <v>1</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="3">
         <v>0.75</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H90" t="s">
-        <v>14</v>
-      </c>
-      <c r="I90" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I90" s="4"/>
       <c r="J90">
         <v>0</v>
       </c>
-      <c r="K90" s="2">
+      <c r="K90" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B91" t="s">
-        <v>120</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -3938,32 +4521,32 @@
       <c r="E91">
         <v>7</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="3">
         <v>7</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
-        <v>14</v>
-      </c>
-      <c r="I91" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I91" s="4"/>
       <c r="J91">
         <v>6</v>
       </c>
-      <c r="K91" s="2">
+      <c r="K91" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B92" t="s">
-        <v>120</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="D92" s="1">
         <v>0.185</v>
@@ -3971,32 +4554,32 @@
       <c r="E92">
         <v>1</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="3">
         <v>0.185</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s">
-        <v>14</v>
-      </c>
-      <c r="I92" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I92" s="4"/>
       <c r="J92">
         <v>1</v>
       </c>
-      <c r="K92" s="2">
+      <c r="K92" s="3">
         <v>0.185</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B93" t="s">
-        <v>120</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -4004,32 +4587,32 @@
       <c r="E93">
         <v>6</v>
       </c>
-      <c r="F93" s="2">
+      <c r="F93" s="3">
         <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s">
-        <v>14</v>
-      </c>
-      <c r="I93" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I93" s="4"/>
       <c r="J93">
         <v>0</v>
       </c>
-      <c r="K93" s="2">
+      <c r="K93" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B94" t="s">
-        <v>120</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>141</v>
+        <v>121</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="D94" s="1">
         <v>0.2</v>
@@ -4037,32 +4620,32 @@
       <c r="E94">
         <v>1</v>
       </c>
-      <c r="F94" s="2">
+      <c r="F94" s="3">
         <v>0.2</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H94" t="s">
-        <v>14</v>
-      </c>
-      <c r="I94" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I94" s="4"/>
       <c r="J94">
         <v>1</v>
       </c>
-      <c r="K94" s="2">
+      <c r="K94" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B95" t="s">
-        <v>120</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -4070,32 +4653,32 @@
       <c r="E95">
         <v>9</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="3">
         <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>14</v>
-      </c>
-      <c r="I95" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I95" s="4"/>
       <c r="J95">
         <v>9</v>
       </c>
-      <c r="K95" s="2">
+      <c r="K95" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B96" t="s">
-        <v>120</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="D96" s="1">
         <v>0.6</v>
@@ -4103,65 +4686,65 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="3">
         <v>0.6</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H96" t="s">
-        <v>14</v>
-      </c>
-      <c r="I96" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I96" s="4"/>
       <c r="J96">
         <v>0</v>
       </c>
-      <c r="K96" s="2">
+      <c r="K96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
-      </c>
-      <c r="C97" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D97" s="1">
+        <v>0.045</v>
+      </c>
+      <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97" s="3">
+        <v>0.045</v>
+      </c>
+      <c r="G97" t="s">
+        <v>16</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="4"/>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97" s="3">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
         <v>143</v>
       </c>
-      <c r="D97" s="1">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="E97">
-        <v>1</v>
-      </c>
-      <c r="F97" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G97" t="s">
-        <v>15</v>
-      </c>
-      <c r="H97" t="s">
-        <v>14</v>
-      </c>
-      <c r="I97" s="3"/>
-      <c r="J97">
-        <v>1</v>
-      </c>
-      <c r="K97" s="2">
-        <v>4.4999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>142</v>
-      </c>
       <c r="B98" t="s">
-        <v>120</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="D98" s="1">
         <v>0.4</v>
@@ -4169,32 +4752,32 @@
       <c r="E98">
         <v>1</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="3">
         <v>0.4</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H98" t="s">
-        <v>14</v>
-      </c>
-      <c r="I98" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I98" s="4"/>
       <c r="J98">
         <v>1</v>
       </c>
-      <c r="K98" s="2">
+      <c r="K98" s="3">
         <v>0.4</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B99" t="s">
-        <v>120</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="D99" s="1">
         <v>0.35</v>
@@ -4202,32 +4785,32 @@
       <c r="E99">
         <v>1</v>
       </c>
-      <c r="F99" s="2">
+      <c r="F99" s="3">
         <v>0.35</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H99" t="s">
-        <v>14</v>
-      </c>
-      <c r="I99" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I99" s="4"/>
       <c r="J99">
         <v>1</v>
       </c>
-      <c r="K99" s="2">
+      <c r="K99" s="3">
         <v>0.35</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="D100" s="1">
         <v>0.12</v>
@@ -4235,32 +4818,32 @@
       <c r="E100">
         <v>1</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="3">
         <v>0.12</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H100" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I100" s="4"/>
       <c r="J100">
         <v>1</v>
       </c>
-      <c r="K100" s="2">
+      <c r="K100" s="3">
         <v>0.12</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>147</v>
+        <v>121</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="D101" s="1">
         <v>0.01</v>
@@ -4268,65 +4851,65 @@
       <c r="E101">
         <v>1</v>
       </c>
-      <c r="F101" s="2">
+      <c r="F101" s="3">
         <v>0.01</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H101" t="s">
-        <v>14</v>
-      </c>
-      <c r="I101" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I101" s="4"/>
       <c r="J101">
         <v>1</v>
       </c>
-      <c r="K101" s="2">
+      <c r="K101" s="3">
         <v>0.01</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B102" t="s">
-        <v>149</v>
-      </c>
-      <c r="C102" s="2" t="s">
         <v>150</v>
       </c>
+      <c r="C102" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="D102" s="1">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
-      <c r="F102" s="2">
-        <v>9.5000000000000001E-2</v>
+      <c r="F102" s="3">
+        <v>0.095</v>
       </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
-      </c>
-      <c r="I102" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I102" s="4"/>
       <c r="J102">
         <v>1</v>
       </c>
-      <c r="K102" s="2">
-        <v>9.5000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K102" s="3">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B103" t="s">
-        <v>149</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="D103" s="1">
         <v>0.21</v>
@@ -4334,32 +4917,32 @@
       <c r="E103">
         <v>2</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="3">
         <v>0.42</v>
       </c>
       <c r="G103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H103" t="s">
-        <v>14</v>
-      </c>
-      <c r="I103" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I103" s="4"/>
       <c r="J103">
         <v>2</v>
       </c>
-      <c r="K103" s="2">
+      <c r="K103" s="3">
         <v>0.42</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B104" t="s">
-        <v>149</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="D104" s="1">
         <v>0.17</v>
@@ -4367,65 +4950,65 @@
       <c r="E104">
         <v>2</v>
       </c>
-      <c r="F104" s="2">
+      <c r="F104" s="3">
         <v>0.34</v>
       </c>
       <c r="G104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H104" t="s">
-        <v>14</v>
-      </c>
-      <c r="I104" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I104" s="4"/>
       <c r="J104">
         <v>2</v>
       </c>
-      <c r="K104" s="2">
+      <c r="K104" s="3">
         <v>0.34</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B105" t="s">
-        <v>149</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="D105" s="1">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
-      <c r="F105" s="2">
-        <v>0.13500000000000001</v>
+      <c r="F105" s="3">
+        <v>0.135</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H105" t="s">
-        <v>14</v>
-      </c>
-      <c r="I105" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I105" s="4"/>
       <c r="J105">
         <v>1</v>
       </c>
-      <c r="K105" s="2">
-        <v>0.13500000000000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K105" s="3">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="D106" s="1">
         <v>0.3</v>
@@ -4433,32 +5016,32 @@
       <c r="E106">
         <v>15</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="3">
         <v>4.5</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>14</v>
-      </c>
-      <c r="I106" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I106" s="4"/>
       <c r="J106">
         <v>15</v>
       </c>
-      <c r="K106" s="2">
+      <c r="K106" s="3">
         <v>4.5</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B107" t="s">
-        <v>149</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="D107" s="1">
         <v>0.34</v>
@@ -4466,32 +5049,32 @@
       <c r="E107">
         <v>1</v>
       </c>
-      <c r="F107" s="2">
+      <c r="F107" s="3">
         <v>0.34</v>
       </c>
       <c r="G107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>14</v>
-      </c>
-      <c r="I107" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I107" s="4"/>
       <c r="J107">
         <v>1</v>
       </c>
-      <c r="K107" s="2">
+      <c r="K107" s="3">
         <v>0.34</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>149</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="D108" s="1">
         <v>0.24</v>
@@ -4499,32 +5082,32 @@
       <c r="E108">
         <v>1</v>
       </c>
-      <c r="F108" s="2">
+      <c r="F108" s="3">
         <v>0.24</v>
       </c>
       <c r="G108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H108" t="s">
-        <v>14</v>
-      </c>
-      <c r="I108" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I108" s="4"/>
       <c r="J108">
         <v>0</v>
       </c>
-      <c r="K108" s="2">
+      <c r="K108" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B109" t="s">
-        <v>149</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="D109" s="1">
         <v>0.15</v>
@@ -4532,32 +5115,32 @@
       <c r="E109">
         <v>3</v>
       </c>
-      <c r="F109" s="2">
-        <v>0.44999999999999996</v>
+      <c r="F109" s="3">
+        <v>0.45</v>
       </c>
       <c r="G109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H109" t="s">
-        <v>14</v>
-      </c>
-      <c r="I109" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I109" s="4"/>
       <c r="J109">
         <v>3</v>
       </c>
-      <c r="K109" s="2">
-        <v>0.44999999999999996</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K109" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B110" t="s">
-        <v>149</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>160</v>
+        <v>150</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="D110" s="1">
         <v>0.157</v>
@@ -4565,65 +5148,65 @@
       <c r="E110">
         <v>2</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="3">
         <v>0.314</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
-        <v>14</v>
-      </c>
-      <c r="I110" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I110" s="4"/>
       <c r="J110">
         <v>2</v>
       </c>
-      <c r="K110" s="2">
+      <c r="K110" s="3">
         <v>0.314</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B111" t="s">
-        <v>149</v>
-      </c>
-      <c r="C111" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0.07</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="4"/>
+      <c r="J111">
+        <v>1</v>
+      </c>
+      <c r="K111" s="3">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
         <v>162</v>
       </c>
-      <c r="D111" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E111">
-        <v>1</v>
-      </c>
-      <c r="F111" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G111" t="s">
-        <v>15</v>
-      </c>
-      <c r="H111" t="s">
-        <v>14</v>
-      </c>
-      <c r="I111" s="3"/>
-      <c r="J111">
-        <v>1</v>
-      </c>
-      <c r="K111" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>161</v>
-      </c>
       <c r="B112" t="s">
-        <v>149</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="D112" s="1">
         <v>0.15</v>
@@ -4631,32 +5214,32 @@
       <c r="E112">
         <v>13</v>
       </c>
-      <c r="F112" s="2">
+      <c r="F112" s="3">
         <v>1.95</v>
       </c>
       <c r="G112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H112" t="s">
-        <v>14</v>
-      </c>
-      <c r="I112" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I112" s="4"/>
       <c r="J112">
         <v>4</v>
       </c>
-      <c r="K112" s="2">
-        <v>0.59999999999999987</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K112" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B113" t="s">
-        <v>149</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="D113" s="1">
         <v>0.158</v>
@@ -4664,65 +5247,65 @@
       <c r="E113">
         <v>15</v>
       </c>
-      <c r="F113" s="2">
+      <c r="F113" s="3">
         <v>2.37</v>
       </c>
       <c r="G113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H113" t="s">
-        <v>14</v>
-      </c>
-      <c r="I113" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I113" s="4"/>
       <c r="J113">
         <v>15</v>
       </c>
-      <c r="K113" s="2">
+      <c r="K113" s="3">
         <v>2.37</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B114" t="s">
-        <v>149</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="D114" s="1">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
-      <c r="F114" s="2">
-        <v>7.5999999999999998E-2</v>
+      <c r="F114" s="3">
+        <v>0.076</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H114" t="s">
-        <v>14</v>
-      </c>
-      <c r="I114" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I114" s="4"/>
       <c r="J114">
         <v>1</v>
       </c>
-      <c r="K114" s="2">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K114" s="3">
+        <v>0.076</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B115" t="s">
-        <v>149</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>166</v>
+        <v>150</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="D115" s="1">
         <v>0.15</v>
@@ -4730,32 +5313,32 @@
       <c r="E115">
         <v>5</v>
       </c>
-      <c r="F115" s="2">
+      <c r="F115" s="3">
         <v>0.75</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H115" t="s">
-        <v>14</v>
-      </c>
-      <c r="I115" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I115" s="4"/>
       <c r="J115">
         <v>5</v>
       </c>
-      <c r="K115" s="2">
+      <c r="K115" s="3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B116" t="s">
-        <v>149</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>167</v>
+        <v>150</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="D116" s="1">
         <v>0.11</v>
@@ -4763,65 +5346,65 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="2">
+      <c r="F116" s="3">
         <v>0.11</v>
       </c>
       <c r="G116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H116" t="s">
-        <v>14</v>
-      </c>
-      <c r="I116" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I116" s="4"/>
       <c r="J116">
         <v>1</v>
       </c>
-      <c r="K116" s="2">
+      <c r="K116" s="3">
         <v>0.11</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B117" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C117" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D117" s="1">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="2">
-        <v>3.5000000000000003E-2</v>
+      <c r="F117" s="3">
+        <v>0.035</v>
       </c>
       <c r="G117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H117" t="s">
-        <v>14</v>
-      </c>
-      <c r="I117" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I117" s="4"/>
       <c r="J117">
         <v>1</v>
       </c>
-      <c r="K117" s="2">
-        <v>3.5000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K117" s="3">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B118" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C118" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D118" s="1">
         <v>0.06</v>
@@ -4829,32 +5412,32 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="2">
+      <c r="F118" s="3">
         <v>0.06</v>
       </c>
       <c r="G118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H118" t="s">
-        <v>14</v>
-      </c>
-      <c r="I118" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I118" s="4"/>
       <c r="J118">
         <v>1</v>
       </c>
-      <c r="K118" s="2">
+      <c r="K118" s="3">
         <v>0.06</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B119" t="s">
-        <v>149</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D119" s="1">
         <v>0.75</v>
@@ -4862,32 +5445,32 @@
       <c r="E119">
         <v>1</v>
       </c>
-      <c r="F119" s="2">
+      <c r="F119" s="3">
         <v>0.75</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
-        <v>14</v>
-      </c>
-      <c r="I119" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I119" s="4"/>
       <c r="J119">
         <v>1</v>
       </c>
-      <c r="K119" s="2">
+      <c r="K119" s="3">
         <v>0.75</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B120" t="s">
-        <v>149</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D120" s="1">
         <v>0.1</v>
@@ -4895,65 +5478,65 @@
       <c r="E120">
         <v>1</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="3">
         <v>0.1</v>
       </c>
       <c r="G120" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H120" t="s">
-        <v>14</v>
-      </c>
-      <c r="I120" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I120" s="4"/>
       <c r="J120">
         <v>1</v>
       </c>
-      <c r="K120" s="2">
+      <c r="K120" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B121" t="s">
+        <v>173</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D121" s="1">
+        <v>0.075</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+      <c r="F121" s="3">
+        <v>0.075</v>
+      </c>
+      <c r="G121" t="s">
+        <v>16</v>
+      </c>
+      <c r="H121" t="s">
+        <v>15</v>
+      </c>
+      <c r="I121" s="4"/>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="K121" s="3">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" t="s">
         <v>172</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D121" s="1">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="E121">
-        <v>1</v>
-      </c>
-      <c r="F121" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G121" t="s">
-        <v>15</v>
-      </c>
-      <c r="H121" t="s">
-        <v>14</v>
-      </c>
-      <c r="I121" s="3"/>
-      <c r="J121">
-        <v>1</v>
-      </c>
-      <c r="K121" s="2">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>171</v>
-      </c>
       <c r="B122" t="s">
-        <v>172</v>
-      </c>
-      <c r="C122" s="2" t="s">
         <v>173</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="D122" s="1">
         <v>0.15</v>
@@ -4961,32 +5544,32 @@
       <c r="E122">
         <v>1</v>
       </c>
-      <c r="F122" s="2">
+      <c r="F122" s="3">
         <v>0.15</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H122" t="s">
-        <v>14</v>
-      </c>
-      <c r="I122" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I122" s="4"/>
       <c r="J122">
         <v>1</v>
       </c>
-      <c r="K122" s="2">
+      <c r="K122" s="3">
         <v>0.15</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B123" t="s">
-        <v>175</v>
-      </c>
-      <c r="C123" s="2" t="s">
         <v>176</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="D123" s="1">
         <v>0.2</v>
@@ -4994,32 +5577,32 @@
       <c r="E123">
         <v>1</v>
       </c>
-      <c r="F123" s="2">
+      <c r="F123" s="3">
         <v>0.2</v>
       </c>
       <c r="G123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H123" t="s">
-        <v>14</v>
-      </c>
-      <c r="I123" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="I123" s="4"/>
       <c r="J123">
         <v>1</v>
       </c>
-      <c r="K123" s="2">
+      <c r="K123" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="D124" s="1">
         <v>1</v>
@@ -5027,34 +5610,34 @@
       <c r="E124">
         <v>20</v>
       </c>
-      <c r="F124" s="2">
+      <c r="F124" s="3">
         <v>20</v>
       </c>
       <c r="G124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H124" t="s">
-        <v>14</v>
-      </c>
-      <c r="I124" s="3">
+        <v>15</v>
+      </c>
+      <c r="I124" s="4">
         <v>44391</v>
       </c>
       <c r="J124">
         <v>20</v>
       </c>
-      <c r="K124" s="2">
+      <c r="K124" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="D125" s="1">
         <v>1</v>
@@ -5062,34 +5645,34 @@
       <c r="E125">
         <v>20</v>
       </c>
-      <c r="F125" s="2">
+      <c r="F125" s="3">
         <v>20</v>
       </c>
       <c r="G125" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H125" t="s">
-        <v>14</v>
-      </c>
-      <c r="I125" s="3">
+        <v>15</v>
+      </c>
+      <c r="I125" s="4">
         <v>44391</v>
       </c>
       <c r="J125">
         <v>20</v>
       </c>
-      <c r="K125" s="2">
+      <c r="K125" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D126" s="1">
         <v>1</v>
@@ -5097,34 +5680,34 @@
       <c r="E126">
         <v>30</v>
       </c>
-      <c r="F126" s="2">
+      <c r="F126" s="3">
         <v>30</v>
       </c>
       <c r="G126" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H126" t="s">
-        <v>14</v>
-      </c>
-      <c r="I126" s="3">
+        <v>15</v>
+      </c>
+      <c r="I126" s="4">
         <v>44391</v>
       </c>
       <c r="J126">
         <v>30</v>
       </c>
-      <c r="K126" s="2">
+      <c r="K126" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B127" t="s">
-        <v>89</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>179</v>
+        <v>90</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D127" s="1">
         <v>0.09</v>
@@ -5132,69 +5715,69 @@
       <c r="E127">
         <v>100</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="3">
         <v>9</v>
       </c>
       <c r="G127" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H127" t="s">
-        <v>14</v>
-      </c>
-      <c r="I127" s="3">
+        <v>15</v>
+      </c>
+      <c r="I127" s="4">
         <v>44391</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
-      <c r="K127" s="2">
+      <c r="K127" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B128" t="s">
-        <v>89</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>181</v>
+        <v>90</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="D128" s="1">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="E128">
         <v>50</v>
       </c>
-      <c r="F128" s="2">
-        <v>7.2499999999999991</v>
+      <c r="F128" s="3">
+        <v>7.25</v>
       </c>
       <c r="G128" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H128" t="s">
-        <v>14</v>
-      </c>
-      <c r="I128" s="3">
+        <v>15</v>
+      </c>
+      <c r="I128" s="4">
         <v>44391</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
-      <c r="K128" s="2">
+      <c r="K128" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B129" t="s">
-        <v>89</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>183</v>
+        <v>90</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D129" s="1">
         <v>0.1</v>
@@ -5202,34 +5785,34 @@
       <c r="E129">
         <v>50</v>
       </c>
-      <c r="F129" s="2">
+      <c r="F129" s="3">
         <v>5</v>
       </c>
       <c r="G129" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H129" t="s">
-        <v>14</v>
-      </c>
-      <c r="I129" s="3">
+        <v>15</v>
+      </c>
+      <c r="I129" s="4">
         <v>44391</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
-      <c r="K129" s="2">
+      <c r="K129" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B130" t="s">
-        <v>89</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D130" s="1">
         <v>0.125</v>
@@ -5237,34 +5820,34 @@
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="F130" s="2">
+      <c r="F130" s="3">
         <v>0.125</v>
       </c>
       <c r="G130" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H130">
         <v>2101546</v>
       </c>
-      <c r="I130" s="3">
+      <c r="I130" s="4">
         <v>44396</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
-      <c r="K130" s="2">
+      <c r="K130" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B131" t="s">
-        <v>89</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="D131" s="1">
         <v>0.104</v>
@@ -5272,34 +5855,34 @@
       <c r="E131">
         <v>1</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="3">
         <v>0.104</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H131">
         <v>2101546</v>
       </c>
-      <c r="I131" s="3">
+      <c r="I131" s="4">
         <v>44396</v>
       </c>
       <c r="J131">
         <v>1</v>
       </c>
-      <c r="K131" s="2">
+      <c r="K131" s="3">
         <v>0.104</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D132" s="1">
         <v>40</v>
@@ -5307,34 +5890,34 @@
       <c r="E132">
         <v>1</v>
       </c>
-      <c r="F132" s="2">
+      <c r="F132" s="3">
         <v>40</v>
       </c>
       <c r="G132" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H132">
         <v>2101128</v>
       </c>
-      <c r="I132" s="3">
+      <c r="I132" s="4">
         <v>44344</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
-      <c r="K132" s="2">
+      <c r="K132" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B133" t="s">
-        <v>31</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>46</v>
+        <v>32</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D133" s="1">
         <v>0.9</v>
@@ -5342,34 +5925,34 @@
       <c r="E133">
         <v>1</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="3">
         <v>0.9</v>
       </c>
       <c r="G133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H133">
         <v>2101982</v>
       </c>
-      <c r="I133" s="3">
+      <c r="I133" s="4">
         <v>44484</v>
       </c>
       <c r="J133">
         <v>1</v>
       </c>
-      <c r="K133" s="2">
+      <c r="K133" s="3">
         <v>0.9</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B134" t="s">
-        <v>120</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D134" s="1">
         <v>0.08</v>
@@ -5377,69 +5960,69 @@
       <c r="E134">
         <v>4</v>
       </c>
-      <c r="F134" s="2">
+      <c r="F134" s="3">
         <v>0.32</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H134">
         <v>2102185</v>
       </c>
-      <c r="I134" s="3">
+      <c r="I134" s="4">
         <v>44510</v>
       </c>
       <c r="J134">
         <v>4</v>
       </c>
-      <c r="K134" s="2">
+      <c r="K134" s="3">
         <v>0.32</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B135" t="s">
-        <v>89</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D135" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="E135">
         <v>1</v>
       </c>
-      <c r="F135" s="2">
-        <v>7.0000000000000007E-2</v>
+      <c r="F135" s="3">
+        <v>0.07</v>
       </c>
       <c r="G135" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H135">
         <v>2102356</v>
       </c>
-      <c r="I135" s="3">
+      <c r="I135" s="4">
         <v>44531</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
-      <c r="K135" s="2">
+      <c r="K135" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B136" t="s">
-        <v>120</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="D136" s="1">
         <v>1</v>
@@ -5447,34 +6030,34 @@
       <c r="E136">
         <v>20</v>
       </c>
-      <c r="F136" s="2">
+      <c r="F136" s="3">
         <v>20</v>
       </c>
       <c r="G136" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H136" t="s">
-        <v>185</v>
-      </c>
-      <c r="I136" s="3">
+        <v>186</v>
+      </c>
+      <c r="I136" s="4">
         <v>44581</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
-      <c r="K136" s="2">
+      <c r="K136" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D137" s="1">
         <v>100</v>
@@ -5482,34 +6065,34 @@
       <c r="E137">
         <v>2</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="3">
         <v>200</v>
       </c>
       <c r="G137" t="s">
+        <v>187</v>
+      </c>
+      <c r="H137" t="s">
         <v>186</v>
       </c>
-      <c r="H137" t="s">
-        <v>185</v>
-      </c>
-      <c r="I137" s="3">
+      <c r="I137" s="4">
         <v>44588</v>
       </c>
       <c r="J137">
         <v>2</v>
       </c>
-      <c r="K137" s="2">
+      <c r="K137" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D138" s="1">
         <v>100</v>
@@ -5517,34 +6100,34 @@
       <c r="E138">
         <v>2</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="3">
         <v>200</v>
       </c>
       <c r="G138" t="s">
+        <v>187</v>
+      </c>
+      <c r="H138" t="s">
         <v>186</v>
       </c>
-      <c r="H138" t="s">
-        <v>185</v>
-      </c>
-      <c r="I138" s="3">
+      <c r="I138" s="4">
         <v>44588</v>
       </c>
       <c r="J138">
         <v>1</v>
       </c>
-      <c r="K138" s="2">
+      <c r="K138" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D139" s="1">
         <v>100</v>
@@ -5552,34 +6135,34 @@
       <c r="E139">
         <v>2</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="3">
         <v>200</v>
       </c>
       <c r="G139" t="s">
+        <v>187</v>
+      </c>
+      <c r="H139" t="s">
         <v>186</v>
       </c>
-      <c r="H139" t="s">
-        <v>185</v>
-      </c>
-      <c r="I139" s="3">
+      <c r="I139" s="4">
         <v>44588</v>
       </c>
       <c r="J139">
         <v>2</v>
       </c>
-      <c r="K139" s="2">
+      <c r="K139" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="D140" s="1">
         <v>100</v>
@@ -5587,34 +6170,34 @@
       <c r="E140">
         <v>2</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="3">
         <v>200</v>
       </c>
       <c r="G140" t="s">
+        <v>187</v>
+      </c>
+      <c r="H140" t="s">
         <v>186</v>
       </c>
-      <c r="H140" t="s">
-        <v>185</v>
-      </c>
-      <c r="I140" s="3">
+      <c r="I140" s="4">
         <v>44588</v>
       </c>
       <c r="J140">
         <v>2</v>
       </c>
-      <c r="K140" s="2">
+      <c r="K140" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D141" s="1">
         <v>100</v>
@@ -5622,34 +6205,34 @@
       <c r="E141">
         <v>2</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="3">
         <v>200</v>
       </c>
       <c r="G141" t="s">
+        <v>187</v>
+      </c>
+      <c r="H141" t="s">
         <v>186</v>
       </c>
-      <c r="H141" t="s">
-        <v>185</v>
-      </c>
-      <c r="I141" s="3">
+      <c r="I141" s="4">
         <v>44588</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
-      <c r="K141" s="2">
+      <c r="K141" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B142" t="s">
-        <v>89</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>179</v>
+        <v>90</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="D142" s="1">
         <v>0.09</v>
@@ -5657,69 +6240,69 @@
       <c r="E142">
         <v>100</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="3">
         <v>9</v>
       </c>
       <c r="G142" t="s">
+        <v>187</v>
+      </c>
+      <c r="H142" t="s">
         <v>186</v>
       </c>
-      <c r="H142" t="s">
-        <v>185</v>
-      </c>
-      <c r="I142" s="3">
+      <c r="I142" s="4">
         <v>44588</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
-      <c r="K142" s="2">
+      <c r="K142" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>181</v>
+        <v>90</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="D143" s="1">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="E143">
         <v>50</v>
       </c>
-      <c r="F143" s="2">
-        <v>7.2499999999999991</v>
+      <c r="F143" s="3">
+        <v>7.25</v>
       </c>
       <c r="G143" t="s">
+        <v>187</v>
+      </c>
+      <c r="H143" t="s">
         <v>186</v>
       </c>
-      <c r="H143" t="s">
-        <v>185</v>
-      </c>
-      <c r="I143" s="3">
+      <c r="I143" s="4">
         <v>44588</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
-      <c r="K143" s="2">
+      <c r="K143" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B144" t="s">
-        <v>89</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>183</v>
+        <v>90</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D144" s="1">
         <v>0.1</v>
@@ -5727,34 +6310,34 @@
       <c r="E144">
         <v>50</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="3">
         <v>5</v>
       </c>
       <c r="G144" t="s">
+        <v>187</v>
+      </c>
+      <c r="H144" t="s">
         <v>186</v>
       </c>
-      <c r="H144" t="s">
-        <v>185</v>
-      </c>
-      <c r="I144" s="3">
+      <c r="I144" s="4">
         <v>44588</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
-      <c r="K144" s="2">
+      <c r="K144" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D145" s="1">
         <v>40</v>
@@ -5762,34 +6345,34 @@
       <c r="E145">
         <v>1</v>
       </c>
-      <c r="F145" s="2">
+      <c r="F145" s="3">
         <v>40</v>
       </c>
       <c r="G145" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H145">
         <v>2200205</v>
       </c>
-      <c r="I145" s="3">
+      <c r="I145" s="4">
         <v>44599</v>
       </c>
       <c r="J145">
         <v>1</v>
       </c>
-      <c r="K145" s="2">
+      <c r="K145" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B146" t="s">
-        <v>89</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="D146" s="1">
         <v>0.04</v>
@@ -5797,139 +6380,139 @@
       <c r="E146">
         <v>1</v>
       </c>
-      <c r="F146" s="2">
+      <c r="F146" s="3">
         <v>0.04</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H146">
         <v>2200264</v>
       </c>
-      <c r="I146" s="3">
+      <c r="I146" s="4">
         <v>44606</v>
       </c>
       <c r="J146">
         <v>1</v>
       </c>
-      <c r="K146" s="2">
+      <c r="K146" s="3">
         <v>0.04</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B147" t="s">
-        <v>120</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="D147" s="1">
-        <v>0.79500000000000004</v>
+        <v>0.795</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
-      <c r="F147" s="2">
-        <v>0.79500000000000004</v>
+      <c r="F147" s="3">
+        <v>0.795</v>
       </c>
       <c r="G147" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H147">
         <v>2200445</v>
       </c>
-      <c r="I147" s="3">
+      <c r="I147" s="4">
         <v>44624</v>
       </c>
       <c r="J147">
         <v>1</v>
       </c>
-      <c r="K147" s="2">
-        <v>0.79500000000000004</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K147" s="3">
+        <v>0.795</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B148" t="s">
-        <v>120</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="D148" s="1">
-        <v>0.39500000000000002</v>
+        <v>0.395</v>
       </c>
       <c r="E148">
         <v>1</v>
       </c>
-      <c r="F148" s="2">
-        <v>0.39500000000000002</v>
+      <c r="F148" s="3">
+        <v>0.395</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H148">
         <v>2200445</v>
       </c>
-      <c r="I148" s="3">
+      <c r="I148" s="4">
         <v>44624</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
-      <c r="K148" s="2">
+      <c r="K148" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B149" t="s">
-        <v>89</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>183</v>
+        <v>90</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D149" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="E149">
         <v>1</v>
       </c>
-      <c r="F149" s="2">
-        <v>7.0000000000000007E-2</v>
+      <c r="F149" s="3">
+        <v>0.07</v>
       </c>
       <c r="G149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H149">
         <v>2200544</v>
       </c>
-      <c r="I149" s="3">
+      <c r="I149" s="4">
         <v>44636</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
-      <c r="K149" s="2">
+      <c r="K149" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B150" t="s">
-        <v>120</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="D150" s="1">
         <v>0.52</v>
@@ -5937,34 +6520,34 @@
       <c r="E150">
         <v>1</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="3">
         <v>0.52</v>
       </c>
       <c r="G150" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H150">
         <v>2200679</v>
       </c>
-      <c r="I150" s="3">
+      <c r="I150" s="4">
         <v>44649</v>
       </c>
       <c r="J150">
         <v>1</v>
       </c>
-      <c r="K150" s="2">
+      <c r="K150" s="3">
         <v>0.52</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="D151" s="1">
         <v>100</v>
@@ -5972,34 +6555,34 @@
       <c r="E151">
         <v>2</v>
       </c>
-      <c r="F151" s="2">
+      <c r="F151" s="3">
         <v>200</v>
       </c>
       <c r="G151" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H151" t="s">
-        <v>185</v>
-      </c>
-      <c r="I151" s="3">
+        <v>186</v>
+      </c>
+      <c r="I151" s="4">
         <v>44716</v>
       </c>
       <c r="J151">
         <v>2</v>
       </c>
-      <c r="K151" s="2">
+      <c r="K151" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>179</v>
+        <v>90</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="D152" s="1">
         <v>0.09</v>
@@ -6007,69 +6590,69 @@
       <c r="E152">
         <v>150</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="3">
         <v>13.5</v>
       </c>
       <c r="G152" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H152" t="s">
-        <v>185</v>
-      </c>
-      <c r="I152" s="3">
+        <v>186</v>
+      </c>
+      <c r="I152" s="4">
         <v>44716</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
-      <c r="K152" s="2">
+      <c r="K152" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B153" t="s">
-        <v>89</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>181</v>
+        <v>90</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="D153" s="1">
-        <v>0.14499999999999999</v>
+        <v>0.145</v>
       </c>
       <c r="E153">
         <v>100</v>
       </c>
-      <c r="F153" s="2">
-        <v>14.499999999999998</v>
+      <c r="F153" s="3">
+        <v>14.5</v>
       </c>
       <c r="G153" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H153" t="s">
-        <v>185</v>
-      </c>
-      <c r="I153" s="3">
+        <v>186</v>
+      </c>
+      <c r="I153" s="4">
         <v>44716</v>
       </c>
       <c r="J153">
         <v>51</v>
       </c>
-      <c r="K153" s="2">
-        <v>7.3949999999999978</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K153" s="3">
+        <v>7.395</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>183</v>
+        <v>90</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="D154" s="1">
         <v>0.1</v>
@@ -6077,34 +6660,34 @@
       <c r="E154">
         <v>150</v>
       </c>
-      <c r="F154" s="2">
+      <c r="F154" s="3">
         <v>15</v>
       </c>
       <c r="G154" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H154" t="s">
-        <v>185</v>
-      </c>
-      <c r="I154" s="3">
+        <v>186</v>
+      </c>
+      <c r="I154" s="4">
         <v>44716</v>
       </c>
       <c r="J154">
         <v>67</v>
       </c>
-      <c r="K154" s="2">
-        <v>6.6999999999999993</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K154" s="3">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>189</v>
+        <v>150</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="D155" s="1">
         <v>0.3</v>
@@ -6112,34 +6695,34 @@
       <c r="E155">
         <v>2</v>
       </c>
-      <c r="F155" s="2">
+      <c r="F155" s="3">
         <v>0.6</v>
       </c>
       <c r="G155" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H155" t="s">
-        <v>185</v>
-      </c>
-      <c r="I155" s="3">
+        <v>186</v>
+      </c>
+      <c r="I155" s="4">
         <v>44716</v>
       </c>
       <c r="J155">
         <v>0</v>
       </c>
-      <c r="K155" s="2">
+      <c r="K155" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B156" t="s">
-        <v>149</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>191</v>
+        <v>150</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="D156" s="1">
         <v>0.3</v>
@@ -6147,34 +6730,34 @@
       <c r="E156">
         <v>2</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="3">
         <v>0.6</v>
       </c>
       <c r="G156" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H156" t="s">
-        <v>185</v>
-      </c>
-      <c r="I156" s="3">
+        <v>186</v>
+      </c>
+      <c r="I156" s="4">
         <v>44716</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
-      <c r="K156" s="2">
+      <c r="K156" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B157" t="s">
-        <v>120</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="D157" s="1">
         <v>0.5</v>
@@ -6182,34 +6765,34 @@
       <c r="E157">
         <v>1</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="3">
         <v>0.5</v>
       </c>
       <c r="G157" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H157">
         <v>2201708</v>
       </c>
-      <c r="I157" s="3">
+      <c r="I157" s="4">
         <v>44756</v>
       </c>
       <c r="J157">
         <v>1</v>
       </c>
-      <c r="K157" s="2">
+      <c r="K157" s="3">
         <v>0.5</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B158" t="s">
-        <v>120</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>143</v>
+        <v>121</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="D158" s="1">
         <v>0.19</v>
@@ -6217,34 +6800,34 @@
       <c r="E158">
         <v>1</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="3">
         <v>0.19</v>
       </c>
       <c r="G158" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H158">
         <v>2201942</v>
       </c>
-      <c r="I158" s="3">
+      <c r="I158" s="4">
         <v>44781</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
-      <c r="K158" s="2">
+      <c r="K158" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="D159" s="1">
         <v>50</v>
@@ -6252,34 +6835,34 @@
       <c r="E159">
         <v>1</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="3">
         <v>50</v>
       </c>
       <c r="G159" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H159">
         <v>2202187</v>
       </c>
-      <c r="I159" s="3">
+      <c r="I159" s="4">
         <v>44803</v>
       </c>
       <c r="J159">
         <v>1</v>
       </c>
-      <c r="K159" s="2">
+      <c r="K159" s="3">
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B160" t="s">
-        <v>89</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>179</v>
+        <v>90</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="D160" s="1">
         <v>0.09</v>
@@ -6287,34 +6870,34 @@
       <c r="E160">
         <v>300</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="3">
         <v>27</v>
       </c>
       <c r="G160" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H160" t="s">
-        <v>185</v>
-      </c>
-      <c r="I160" s="3">
+        <v>186</v>
+      </c>
+      <c r="I160" s="4">
         <v>44792</v>
       </c>
       <c r="J160">
         <v>211</v>
       </c>
-      <c r="K160" s="2">
-        <v>18.990000000000002</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K160" s="3">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B161" t="s">
-        <v>120</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="D161" s="1">
         <v>1</v>
@@ -6322,34 +6905,34 @@
       <c r="E161">
         <v>9</v>
       </c>
-      <c r="F161" s="2">
+      <c r="F161" s="3">
         <v>9</v>
       </c>
       <c r="G161" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H161" t="s">
-        <v>185</v>
-      </c>
-      <c r="I161" s="3">
+        <v>186</v>
+      </c>
+      <c r="I161" s="4">
         <v>44881</v>
       </c>
       <c r="J161">
         <v>0</v>
       </c>
-      <c r="K161" s="2">
+      <c r="K161" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B162" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C162" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D162" s="1">
         <v>0.1</v>
@@ -6357,34 +6940,34 @@
       <c r="E162">
         <v>1</v>
       </c>
-      <c r="F162" s="2">
+      <c r="F162" s="3">
         <v>0.1</v>
       </c>
       <c r="G162" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H162">
         <v>2202927</v>
       </c>
-      <c r="I162" s="3">
+      <c r="I162" s="4">
         <v>44875</v>
       </c>
       <c r="J162">
         <v>1</v>
       </c>
-      <c r="K162" s="2">
+      <c r="K162" s="3">
         <v>0.1</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D163" s="1">
         <v>30</v>
@@ -6392,34 +6975,34 @@
       <c r="E163">
         <v>1</v>
       </c>
-      <c r="F163" s="2">
+      <c r="F163" s="3">
         <v>30</v>
       </c>
       <c r="G163" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H163">
         <v>2202951</v>
       </c>
-      <c r="I163" s="3">
+      <c r="I163" s="4">
         <v>44879</v>
       </c>
       <c r="J163">
         <v>1</v>
       </c>
-      <c r="K163" s="2">
+      <c r="K163" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D164" s="1">
         <v>20</v>
@@ -6427,26 +7010,27 @@
       <c r="E164">
         <v>1</v>
       </c>
-      <c r="F164" s="2">
+      <c r="F164" s="3">
         <v>20</v>
       </c>
       <c r="G164" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H164">
         <v>2202951</v>
       </c>
-      <c r="I164" s="3">
+      <c r="I164" s="4">
         <v>44879</v>
       </c>
       <c r="J164">
         <v>1</v>
       </c>
-      <c r="K164" s="2">
+      <c r="K164" s="3">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>